--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -19,75 +19,87 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+  <x:si>
+    <x:t>Icon/Icon_skill_explosion_01</x:t>
+  </x:si>
   <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
+    <x:t>skill_fireball_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적을 벨 수 있는 검기를 날린다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불로 된 구체를 만들어 날린다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_fireball_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_explosion_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_swing_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어볼!!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일단 휘두르기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>커피 마시기</x:t>
+  </x:si>
+  <x:si>
     <x:t>익스플로젼</x:t>
   </x:si>
   <x:si>
-    <x:t>파이어볼!!</x:t>
+    <x:t>풀 스윙</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대 폭 발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>검기 날리기</x:t>
   </x:si>
   <x:si>
     <x:t>파이어볼</x:t>
   </x:si>
   <x:si>
-    <x:t>대 폭 발</x:t>
-  </x:si>
-  <x:si>
-    <x:t>풀 스윙</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>커피 마시기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일단 휘두르기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>검기 날리기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불로 된 구체를 만들어 날린다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_fireball_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적을 벨 수 있는 검기를 날린다.</x:t>
+    <x:t>Icon/icon_skill_fireball_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_skill_swing_01</x:t>
   </x:si>
   <x:si>
     <x:t>커피를 볶아 마신다. 모든 상태이상이 해제된다.</x:t>
   </x:si>
   <x:si>
+    <x:t>skill_normalSword_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>skill_rest_coffee_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_normalSword_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Skill_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Skill_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Skill_3</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -223,7 +235,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -264,6 +276,9 @@
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
@@ -876,6 +891,7 @@
     <x:col min="1" max="1" width="23" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="19.5703125" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="50.7109375" style="1" customWidth="1"/>
+    <x:col min="4" max="4" width="28.5703125" customWidth="1"/>
     <x:col min="5" max="5" width="30.5703125" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -886,39 +902,44 @@
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
     </x:row>
-    <x:row r="2" spans="1:3" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A2" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B2" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:3" ht="15.75" customHeight="1">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A3" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D3" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D4" s="4"/>
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="E4" s="4"/>
       <x:c r="F4" s="4"/>
       <x:c r="G4" s="4"/>
@@ -933,15 +954,14 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="5" t="s">
-        <x:v>19</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D5" s="4"/>
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="E5" s="4"/>
       <x:c r="F5" s="4"/>
       <x:c r="G5" s="4"/>
@@ -956,15 +976,14 @@
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>18</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D6" s="4"/>
+        <x:v>24</x:v>
+      </x:c>
       <x:c r="E6" s="4"/>
       <x:c r="F6" s="4"/>
       <x:c r="G6" s="4"/>
@@ -979,15 +998,17 @@
     </x:row>
     <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A7" s="13" t="s">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B7" s="13" t="s">
-        <x:v>5</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="13" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D7" s="4"/>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
       <x:c r="E7" s="4"/>
       <x:c r="F7" s="4"/>
       <x:c r="G7" s="4"/>
@@ -1002,15 +1023,17 @@
     </x:row>
     <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A8" s="13" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B8" s="13" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B8" s="13" t="s">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="C8" s="13" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="4"/>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="E8" s="4"/>
       <x:c r="F8" s="4"/>
       <x:c r="G8" s="4"/>
@@ -1025,15 +1048,17 @@
     </x:row>
     <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A9" s="13" t="s">
-        <x:v>22</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B9" s="13" t="s">
-        <x:v>1</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="13" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D9" s="4"/>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="E9" s="4"/>
       <x:c r="F9" s="4"/>
       <x:c r="G9" s="4"/>
@@ -2220,7 +2245,7 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="19410" windowHeight="9945"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="21900" windowHeight="9945"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -21,85 +21,85 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
   <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적을 벨 수 있는 검기를 날린다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_fireball_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불로 된 구체를 만들어 날린다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_explosion_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_fireball_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_swing_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>Icon/Icon_skill_explosion_01</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_fireball_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적을 벨 수 있는 검기를 날린다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불로 된 구체를 만들어 날린다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_fireball_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_explosion_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_swing_01</x:t>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_normalSword_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_rest_coffee_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일단 휘두르기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어볼!!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>커피 마시기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대 폭 발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>익스플로젼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>풀 스윙</x:t>
+  </x:si>
+  <x:si>
+    <x:t>검기 날리기</x:t>
   </x:si>
   <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
     <x:t>IconPath</x:t>
   </x:si>
   <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어볼!!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일단 휘두르기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>커피 마시기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>익스플로젼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>풀 스윙</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대 폭 발</x:t>
-  </x:si>
-  <x:si>
-    <x:t>검기 날리기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어볼</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/icon_skill_fireball_02</x:t>
   </x:si>
   <x:si>
+    <x:t>커피를 볶아 마신다. 모든 상태이상이 해제된다.</x:t>
+  </x:si>
+  <x:si>
     <x:t>Icon/Icon_skill_swing_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>커피를 볶아 마신다. 모든 상태이상이 해제된다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_normalSword_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_rest_coffee_01</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -235,7 +235,10 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="15">
+  <x:cellXfs count="16">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -888,396 +891,396 @@
   <x:dimension ref="A1:O35"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
-    <x:col min="1" max="1" width="23" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="19.5703125" style="1" customWidth="1"/>
-    <x:col min="3" max="3" width="50.7109375" style="1" customWidth="1"/>
-    <x:col min="4" max="4" width="28.5703125" customWidth="1"/>
-    <x:col min="5" max="5" width="30.5703125" style="1" customWidth="1"/>
+    <x:col min="1" max="1" width="23" style="2" customWidth="1"/>
+    <x:col min="2" max="2" width="19.5703125" style="2" customWidth="1"/>
+    <x:col min="3" max="3" width="50.7109375" style="2" customWidth="1"/>
+    <x:col min="4" max="4" width="28.5703125" style="1" customWidth="1"/>
+    <x:col min="5" max="5" width="30.5703125" style="2" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A1" s="2" t="s">
+      <x:c r="A1" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B1" s="3"/>
+      <x:c r="C1" s="3"/>
+    </x:row>
+    <x:row r="2" spans="1:4" ht="15.75" customHeight="1">
+      <x:c r="A2" s="3" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B2" s="3" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C2" s="3" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:4" ht="15.75" customHeight="1">
+      <x:c r="A3" s="4" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B3" s="4" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A4" s="6" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E4" s="5"/>
+      <x:c r="F4" s="5"/>
+      <x:c r="G4" s="5"/>
+      <x:c r="H4" s="5"/>
+      <x:c r="I4" s="5"/>
+      <x:c r="J4" s="5"/>
+      <x:c r="K4" s="5"/>
+      <x:c r="L4" s="5"/>
+      <x:c r="M4" s="5"/>
+      <x:c r="N4" s="5"/>
+      <x:c r="O4" s="5"/>
+    </x:row>
+    <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A5" s="6" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C5" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E5" s="5"/>
+      <x:c r="F5" s="5"/>
+      <x:c r="G5" s="5"/>
+      <x:c r="H5" s="5"/>
+      <x:c r="I5" s="5"/>
+      <x:c r="J5" s="5"/>
+      <x:c r="K5" s="5"/>
+      <x:c r="L5" s="5"/>
+      <x:c r="M5" s="5"/>
+      <x:c r="N5" s="5"/>
+      <x:c r="O5" s="5"/>
+    </x:row>
+    <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A6" s="7" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C6" s="7" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E6" s="5"/>
+      <x:c r="F6" s="5"/>
+      <x:c r="G6" s="5"/>
+      <x:c r="H6" s="5"/>
+      <x:c r="I6" s="5"/>
+      <x:c r="J6" s="5"/>
+      <x:c r="K6" s="5"/>
+      <x:c r="L6" s="5"/>
+      <x:c r="M6" s="5"/>
+      <x:c r="N6" s="5"/>
+      <x:c r="O6" s="5"/>
+    </x:row>
+    <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A7" s="14" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D7" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E7" s="5"/>
+      <x:c r="F7" s="5"/>
+      <x:c r="G7" s="5"/>
+      <x:c r="H7" s="5"/>
+      <x:c r="I7" s="5"/>
+      <x:c r="J7" s="5"/>
+      <x:c r="K7" s="5"/>
+      <x:c r="L7" s="5"/>
+      <x:c r="M7" s="5"/>
+      <x:c r="N7" s="5"/>
+      <x:c r="O7" s="5"/>
+    </x:row>
+    <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A8" s="14" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B1" s="2"/>
-      <x:c r="C1" s="2"/>
-    </x:row>
-    <x:row r="2" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A2" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B2" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C2" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A3" s="3" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B3" s="3" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D3" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A4" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B4" s="5" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C4" s="5" t="s">
+      <x:c r="D8" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E8" s="5"/>
+      <x:c r="F8" s="5"/>
+      <x:c r="G8" s="5"/>
+      <x:c r="H8" s="5"/>
+      <x:c r="I8" s="5"/>
+      <x:c r="J8" s="5"/>
+      <x:c r="K8" s="5"/>
+      <x:c r="L8" s="5"/>
+      <x:c r="M8" s="5"/>
+      <x:c r="N8" s="5"/>
+      <x:c r="O8" s="5"/>
+    </x:row>
+    <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A9" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E4" s="4"/>
-      <x:c r="F4" s="4"/>
-      <x:c r="G4" s="4"/>
-      <x:c r="H4" s="4"/>
-      <x:c r="I4" s="4"/>
-      <x:c r="J4" s="4"/>
-      <x:c r="K4" s="4"/>
-      <x:c r="L4" s="4"/>
-      <x:c r="M4" s="4"/>
-      <x:c r="N4" s="4"/>
-      <x:c r="O4" s="4"/>
-    </x:row>
-    <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A5" s="5" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B5" s="6" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C5" s="6" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="4"/>
-      <x:c r="F5" s="4"/>
-      <x:c r="G5" s="4"/>
-      <x:c r="H5" s="4"/>
-      <x:c r="I5" s="4"/>
-      <x:c r="J5" s="4"/>
-      <x:c r="K5" s="4"/>
-      <x:c r="L5" s="4"/>
-      <x:c r="M5" s="4"/>
-      <x:c r="N5" s="4"/>
-      <x:c r="O5" s="4"/>
-    </x:row>
-    <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A6" s="6" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B6" s="6" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C6" s="6" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E6" s="4"/>
-      <x:c r="F6" s="4"/>
-      <x:c r="G6" s="4"/>
-      <x:c r="H6" s="4"/>
-      <x:c r="I6" s="4"/>
-      <x:c r="J6" s="4"/>
-      <x:c r="K6" s="4"/>
-      <x:c r="L6" s="4"/>
-      <x:c r="M6" s="4"/>
-      <x:c r="N6" s="4"/>
-      <x:c r="O6" s="4"/>
-    </x:row>
-    <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A7" s="13" t="s">
+      <x:c r="C9" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B7" s="13" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C7" s="13" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D7" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E7" s="4"/>
-      <x:c r="F7" s="4"/>
-      <x:c r="G7" s="4"/>
-      <x:c r="H7" s="4"/>
-      <x:c r="I7" s="4"/>
-      <x:c r="J7" s="4"/>
-      <x:c r="K7" s="4"/>
-      <x:c r="L7" s="4"/>
-      <x:c r="M7" s="4"/>
-      <x:c r="N7" s="4"/>
-      <x:c r="O7" s="4"/>
-    </x:row>
-    <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A8" s="13" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B8" s="13" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C8" s="13" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E8" s="4"/>
-      <x:c r="F8" s="4"/>
-      <x:c r="G8" s="4"/>
-      <x:c r="H8" s="4"/>
-      <x:c r="I8" s="4"/>
-      <x:c r="J8" s="4"/>
-      <x:c r="K8" s="4"/>
-      <x:c r="L8" s="4"/>
-      <x:c r="M8" s="4"/>
-      <x:c r="N8" s="4"/>
-      <x:c r="O8" s="4"/>
-    </x:row>
-    <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A9" s="13" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B9" s="13" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C9" s="13" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E9" s="4"/>
-      <x:c r="F9" s="4"/>
-      <x:c r="G9" s="4"/>
-      <x:c r="H9" s="4"/>
-      <x:c r="I9" s="4"/>
-      <x:c r="J9" s="4"/>
-      <x:c r="K9" s="4"/>
-      <x:c r="L9" s="4"/>
-      <x:c r="M9" s="4"/>
-      <x:c r="N9" s="4"/>
-      <x:c r="O9" s="4"/>
+      <x:c r="E9" s="5"/>
+      <x:c r="F9" s="5"/>
+      <x:c r="G9" s="5"/>
+      <x:c r="H9" s="5"/>
+      <x:c r="I9" s="5"/>
+      <x:c r="J9" s="5"/>
+      <x:c r="K9" s="5"/>
+      <x:c r="L9" s="5"/>
+      <x:c r="M9" s="5"/>
+      <x:c r="N9" s="5"/>
+      <x:c r="O9" s="5"/>
     </x:row>
     <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A10" s="8"/>
-      <x:c r="B10" s="8"/>
-      <x:c r="C10" s="8"/>
-      <x:c r="D10" s="4"/>
-      <x:c r="E10" s="4"/>
-      <x:c r="F10" s="4"/>
-      <x:c r="G10" s="4"/>
-      <x:c r="H10" s="4"/>
-      <x:c r="I10" s="4"/>
-      <x:c r="J10" s="4"/>
-      <x:c r="K10" s="4"/>
-      <x:c r="L10" s="4"/>
-      <x:c r="M10" s="4"/>
-      <x:c r="N10" s="4"/>
-      <x:c r="O10" s="4"/>
+      <x:c r="A10" s="9"/>
+      <x:c r="B10" s="9"/>
+      <x:c r="C10" s="9"/>
+      <x:c r="D10" s="5"/>
+      <x:c r="E10" s="5"/>
+      <x:c r="F10" s="5"/>
+      <x:c r="G10" s="5"/>
+      <x:c r="H10" s="5"/>
+      <x:c r="I10" s="5"/>
+      <x:c r="J10" s="5"/>
+      <x:c r="K10" s="5"/>
+      <x:c r="L10" s="5"/>
+      <x:c r="M10" s="5"/>
+      <x:c r="N10" s="5"/>
+      <x:c r="O10" s="5"/>
     </x:row>
     <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A11" s="8"/>
-      <x:c r="B11" s="8"/>
-      <x:c r="C11" s="8"/>
-      <x:c r="D11" s="4"/>
-      <x:c r="E11" s="4"/>
-      <x:c r="F11" s="4"/>
-      <x:c r="G11" s="4"/>
-      <x:c r="H11" s="4"/>
-      <x:c r="I11" s="4"/>
-      <x:c r="J11" s="4"/>
-      <x:c r="K11" s="4"/>
-      <x:c r="L11" s="4"/>
-      <x:c r="M11" s="4"/>
-      <x:c r="N11" s="4"/>
-      <x:c r="O11" s="4"/>
+      <x:c r="A11" s="9"/>
+      <x:c r="B11" s="9"/>
+      <x:c r="C11" s="9"/>
+      <x:c r="D11" s="5"/>
+      <x:c r="E11" s="5"/>
+      <x:c r="F11" s="5"/>
+      <x:c r="G11" s="5"/>
+      <x:c r="H11" s="5"/>
+      <x:c r="I11" s="5"/>
+      <x:c r="J11" s="5"/>
+      <x:c r="K11" s="5"/>
+      <x:c r="L11" s="5"/>
+      <x:c r="M11" s="5"/>
+      <x:c r="N11" s="5"/>
+      <x:c r="O11" s="5"/>
     </x:row>
     <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A12" s="7"/>
-      <x:c r="B12" s="7"/>
-      <x:c r="C12" s="7"/>
-      <x:c r="D12" s="4"/>
-      <x:c r="E12" s="4"/>
-      <x:c r="F12" s="4"/>
-      <x:c r="G12" s="4"/>
-      <x:c r="H12" s="4"/>
-      <x:c r="I12" s="4"/>
-      <x:c r="J12" s="4"/>
-      <x:c r="K12" s="4"/>
-      <x:c r="L12" s="4"/>
-      <x:c r="M12" s="4"/>
-      <x:c r="N12" s="4"/>
-      <x:c r="O12" s="4"/>
+      <x:c r="A12" s="8"/>
+      <x:c r="B12" s="8"/>
+      <x:c r="C12" s="8"/>
+      <x:c r="D12" s="5"/>
+      <x:c r="E12" s="5"/>
+      <x:c r="F12" s="5"/>
+      <x:c r="G12" s="5"/>
+      <x:c r="H12" s="5"/>
+      <x:c r="I12" s="5"/>
+      <x:c r="J12" s="5"/>
+      <x:c r="K12" s="5"/>
+      <x:c r="L12" s="5"/>
+      <x:c r="M12" s="5"/>
+      <x:c r="N12" s="5"/>
+      <x:c r="O12" s="5"/>
     </x:row>
     <x:row r="13" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A13" s="5"/>
-      <x:c r="B13" s="5"/>
-      <x:c r="C13" s="5"/>
-      <x:c r="D13" s="4"/>
-      <x:c r="E13" s="4"/>
-      <x:c r="F13" s="4"/>
-      <x:c r="G13" s="4"/>
-      <x:c r="H13" s="4"/>
-      <x:c r="I13" s="4"/>
-      <x:c r="J13" s="4"/>
-      <x:c r="K13" s="4"/>
-      <x:c r="L13" s="4"/>
-      <x:c r="M13" s="4"/>
-      <x:c r="N13" s="4"/>
-      <x:c r="O13" s="4"/>
+      <x:c r="A13" s="6"/>
+      <x:c r="B13" s="6"/>
+      <x:c r="C13" s="6"/>
+      <x:c r="D13" s="5"/>
+      <x:c r="E13" s="5"/>
+      <x:c r="F13" s="5"/>
+      <x:c r="G13" s="5"/>
+      <x:c r="H13" s="5"/>
+      <x:c r="I13" s="5"/>
+      <x:c r="J13" s="5"/>
+      <x:c r="K13" s="5"/>
+      <x:c r="L13" s="5"/>
+      <x:c r="M13" s="5"/>
+      <x:c r="N13" s="5"/>
+      <x:c r="O13" s="5"/>
     </x:row>
     <x:row r="14" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A14" s="8"/>
-      <x:c r="B14" s="8"/>
-      <x:c r="C14" s="8"/>
-      <x:c r="D14" s="4"/>
-      <x:c r="E14" s="4"/>
-      <x:c r="F14" s="4"/>
-      <x:c r="G14" s="4"/>
-      <x:c r="H14" s="4"/>
-      <x:c r="I14" s="4"/>
-      <x:c r="J14" s="4"/>
-      <x:c r="K14" s="4"/>
-      <x:c r="L14" s="4"/>
-      <x:c r="M14" s="4"/>
-      <x:c r="N14" s="4"/>
-      <x:c r="O14" s="4"/>
+      <x:c r="A14" s="9"/>
+      <x:c r="B14" s="9"/>
+      <x:c r="C14" s="9"/>
+      <x:c r="D14" s="5"/>
+      <x:c r="E14" s="5"/>
+      <x:c r="F14" s="5"/>
+      <x:c r="G14" s="5"/>
+      <x:c r="H14" s="5"/>
+      <x:c r="I14" s="5"/>
+      <x:c r="J14" s="5"/>
+      <x:c r="K14" s="5"/>
+      <x:c r="L14" s="5"/>
+      <x:c r="M14" s="5"/>
+      <x:c r="N14" s="5"/>
+      <x:c r="O14" s="5"/>
     </x:row>
     <x:row r="15" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A15" s="8"/>
-      <x:c r="B15" s="8"/>
-      <x:c r="C15" s="8"/>
-      <x:c r="D15" s="4"/>
-      <x:c r="E15" s="4"/>
-      <x:c r="F15" s="4"/>
-      <x:c r="G15" s="4"/>
-      <x:c r="H15" s="4"/>
-      <x:c r="I15" s="4"/>
-      <x:c r="J15" s="4"/>
-      <x:c r="K15" s="4"/>
-      <x:c r="L15" s="4"/>
-      <x:c r="M15" s="4"/>
-      <x:c r="N15" s="4"/>
-      <x:c r="O15" s="4"/>
+      <x:c r="A15" s="9"/>
+      <x:c r="B15" s="9"/>
+      <x:c r="C15" s="9"/>
+      <x:c r="D15" s="5"/>
+      <x:c r="E15" s="5"/>
+      <x:c r="F15" s="5"/>
+      <x:c r="G15" s="5"/>
+      <x:c r="H15" s="5"/>
+      <x:c r="I15" s="5"/>
+      <x:c r="J15" s="5"/>
+      <x:c r="K15" s="5"/>
+      <x:c r="L15" s="5"/>
+      <x:c r="M15" s="5"/>
+      <x:c r="N15" s="5"/>
+      <x:c r="O15" s="5"/>
     </x:row>
     <x:row r="16" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A16" s="9"/>
-      <x:c r="B16" s="9"/>
-      <x:c r="C16" s="9"/>
+      <x:c r="A16" s="10"/>
+      <x:c r="B16" s="10"/>
+      <x:c r="C16" s="10"/>
     </x:row>
     <x:row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A17" s="10"/>
-      <x:c r="B17" s="10"/>
-      <x:c r="C17" s="10"/>
+      <x:c r="A17" s="11"/>
+      <x:c r="B17" s="11"/>
+      <x:c r="C17" s="11"/>
     </x:row>
     <x:row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A18" s="10"/>
-      <x:c r="B18" s="10"/>
-      <x:c r="C18" s="10"/>
+      <x:c r="A18" s="11"/>
+      <x:c r="B18" s="11"/>
+      <x:c r="C18" s="11"/>
     </x:row>
     <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A19" s="10"/>
-      <x:c r="B19" s="10"/>
-      <x:c r="C19" s="10"/>
-      <x:c r="D19" s="4"/>
-      <x:c r="E19" s="4"/>
+      <x:c r="A19" s="11"/>
+      <x:c r="B19" s="11"/>
+      <x:c r="C19" s="11"/>
+      <x:c r="D19" s="5"/>
+      <x:c r="E19" s="5"/>
     </x:row>
     <x:row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A20" s="10"/>
-      <x:c r="B20" s="10"/>
-      <x:c r="C20" s="10"/>
+      <x:c r="A20" s="11"/>
+      <x:c r="B20" s="11"/>
+      <x:c r="C20" s="11"/>
     </x:row>
     <x:row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A21" s="10"/>
-      <x:c r="B21" s="10"/>
-      <x:c r="C21" s="10"/>
+      <x:c r="A21" s="11"/>
+      <x:c r="B21" s="11"/>
+      <x:c r="C21" s="11"/>
     </x:row>
     <x:row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A22" s="10"/>
-      <x:c r="B22" s="10"/>
-      <x:c r="C22" s="10"/>
+      <x:c r="A22" s="11"/>
+      <x:c r="B22" s="11"/>
+      <x:c r="C22" s="11"/>
     </x:row>
     <x:row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A23" s="10"/>
-      <x:c r="B23" s="10"/>
-      <x:c r="C23" s="10"/>
+      <x:c r="A23" s="11"/>
+      <x:c r="B23" s="11"/>
+      <x:c r="C23" s="11"/>
     </x:row>
     <x:row r="24" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A24" s="10"/>
-      <x:c r="B24" s="10"/>
-      <x:c r="C24" s="10"/>
+      <x:c r="A24" s="11"/>
+      <x:c r="B24" s="11"/>
+      <x:c r="C24" s="11"/>
     </x:row>
     <x:row r="25" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A25" s="10"/>
-      <x:c r="B25" s="10"/>
-      <x:c r="C25" s="10"/>
-      <x:c r="E25" s="4"/>
+      <x:c r="A25" s="11"/>
+      <x:c r="B25" s="11"/>
+      <x:c r="C25" s="11"/>
+      <x:c r="E25" s="5"/>
     </x:row>
     <x:row r="26" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A26" s="11"/>
-      <x:c r="B26" s="11"/>
-      <x:c r="C26" s="11"/>
-      <x:c r="E26" s="4"/>
+      <x:c r="A26" s="12"/>
+      <x:c r="B26" s="12"/>
+      <x:c r="C26" s="12"/>
+      <x:c r="E26" s="5"/>
     </x:row>
     <x:row r="27" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A27" s="11"/>
-      <x:c r="B27" s="11"/>
-      <x:c r="C27" s="11"/>
-      <x:c r="E27" s="4"/>
+      <x:c r="A27" s="12"/>
+      <x:c r="B27" s="12"/>
+      <x:c r="C27" s="12"/>
+      <x:c r="E27" s="5"/>
     </x:row>
     <x:row r="28" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A28" s="11"/>
-      <x:c r="B28" s="11"/>
-      <x:c r="C28" s="11"/>
-      <x:c r="E28" s="4"/>
+      <x:c r="A28" s="12"/>
+      <x:c r="B28" s="12"/>
+      <x:c r="C28" s="12"/>
+      <x:c r="E28" s="5"/>
     </x:row>
     <x:row r="29" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A29" s="11"/>
-      <x:c r="B29" s="11"/>
-      <x:c r="C29" s="11"/>
+      <x:c r="A29" s="12"/>
+      <x:c r="B29" s="12"/>
+      <x:c r="C29" s="12"/>
     </x:row>
     <x:row r="30" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A30" s="11"/>
-      <x:c r="B30" s="11"/>
-      <x:c r="C30" s="11"/>
+      <x:c r="A30" s="12"/>
+      <x:c r="B30" s="12"/>
+      <x:c r="C30" s="12"/>
     </x:row>
     <x:row r="31" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A31" s="11"/>
-      <x:c r="B31" s="11"/>
-      <x:c r="C31" s="11"/>
+      <x:c r="A31" s="12"/>
+      <x:c r="B31" s="12"/>
+      <x:c r="C31" s="12"/>
     </x:row>
     <x:row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A32" s="12"/>
-      <x:c r="B32" s="12"/>
-      <x:c r="C32" s="12"/>
+      <x:c r="A32" s="13"/>
+      <x:c r="B32" s="13"/>
+      <x:c r="C32" s="13"/>
     </x:row>
     <x:row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A33" s="12"/>
-      <x:c r="B33" s="12"/>
-      <x:c r="C33" s="12"/>
+      <x:c r="A33" s="13"/>
+      <x:c r="B33" s="13"/>
+      <x:c r="C33" s="13"/>
     </x:row>
     <x:row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A34" s="12"/>
-      <x:c r="B34" s="12"/>
-      <x:c r="C34" s="12"/>
+      <x:c r="A34" s="13"/>
+      <x:c r="B34" s="13"/>
+      <x:c r="C34" s="13"/>
     </x:row>
     <x:row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A35" s="12"/>
-      <x:c r="B35" s="12"/>
-      <x:c r="C35" s="12"/>
+      <x:c r="A35" s="13"/>
+      <x:c r="B35" s="13"/>
+      <x:c r="C35" s="13"/>
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1"/>
     <x:row r="37" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="21900" windowHeight="9945"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9945"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -27,28 +27,64 @@
     <x:t>적을 벨 수 있는 검기를 날린다.</x:t>
   </x:si>
   <x:si>
+    <x:t>불로 된 구체를 만들어 날린다.</x:t>
+  </x:si>
+  <x:si>
     <x:t>skill_fireball_01</x:t>
   </x:si>
   <x:si>
-    <x:t>불로 된 구체를 만들어 날린다.</x:t>
+    <x:t>skill_fireball_02</x:t>
   </x:si>
   <x:si>
     <x:t>skill_explosion_01</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_fireball_02</x:t>
+    <x:t>익스플로젼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>커피 마시기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대 폭 발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일단 휘두르기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>풀 스윙</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어볼!!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>검기 날리기</x:t>
   </x:si>
   <x:si>
     <x:t>skill_swing_01</x:t>
   </x:si>
   <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
     <x:t>Icon/Icon_skill_explosion_01</x:t>
   </x:si>
   <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
     <x:t>캐릭터 고유 ID</x:t>
   </x:si>
   <x:si>
-    <x:t>Description</x:t>
+    <x:t>IconPath</x:t>
   </x:si>
   <x:si>
     <x:t>skill_normalSword_01</x:t>
@@ -57,49 +93,13 @@
     <x:t>skill_rest_coffee_01</x:t>
   </x:si>
   <x:si>
-    <x:t>일단 휘두르기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어볼!!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>커피 마시기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대 폭 발</x:t>
-  </x:si>
-  <x:si>
-    <x:t>익스플로젼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>풀 스윙</x:t>
-  </x:si>
-  <x:si>
-    <x:t>검기 날리기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/icon_skill_fireball_02</x:t>
   </x:si>
   <x:si>
+    <x:t>Icon/Icon_skill_swing_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>커피를 볶아 마신다. 모든 상태이상이 해제된다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_skill_swing_01</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -900,23 +900,23 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
     </x:row>
     <x:row r="2" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A2" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4" ht="15.75" customHeight="1">
@@ -924,24 +924,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B3" s="4" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="C3" s="4" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="6" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="s">
         <x:v>2</x:v>
-      </x:c>
-      <x:c r="B4" s="6" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C4" s="6" t="s">
-        <x:v>3</x:v>
       </x:c>
       <x:c r="E4" s="5"/>
       <x:c r="F4" s="5"/>
@@ -957,10 +957,10 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="6" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B5" s="7" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
         <x:v>1</x:v>
@@ -979,13 +979,13 @@
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="7" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B6" s="7" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C6" s="7" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E6" s="5"/>
       <x:c r="F6" s="5"/>
@@ -1001,16 +1001,16 @@
     </x:row>
     <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A7" s="14" t="s">
-        <x:v>6</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B7" s="14" t="s">
-        <x:v>18</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="14" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D7" s="15" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E7" s="5"/>
       <x:c r="F7" s="5"/>
@@ -1026,13 +1026,13 @@
     </x:row>
     <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A8" s="14" t="s">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="14" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D8" s="15" t="s">
         <x:v>24</x:v>
@@ -1051,16 +1051,16 @@
     </x:row>
     <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A9" s="14" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B9" s="14" t="s">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>15</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E9" s="5"/>
       <x:c r="F9" s="5"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -19,87 +19,99 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+  <x:si>
+    <x:t>CostMp</x:t>
+  </x:si>
   <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_swing_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>적을 벨 수 있는 검기를 날린다.</x:t>
   </x:si>
   <x:si>
+    <x:t>skill_fireball_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>불로 된 구체를 만들어 날린다.</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_fireball_01</x:t>
-  </x:si>
-  <x:si>
     <x:t>skill_fireball_02</x:t>
   </x:si>
   <x:si>
     <x:t>skill_explosion_01</x:t>
   </x:si>
   <x:si>
+    <x:t>대 폭 발</x:t>
+  </x:si>
+  <x:si>
     <x:t>익스플로젼</x:t>
   </x:si>
   <x:si>
+    <x:t>검기 날리기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>커피 마시기</x:t>
+  </x:si>
+  <x:si>
     <x:t>파이어볼</x:t>
   </x:si>
   <x:si>
-    <x:t>커피 마시기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대 폭 발</x:t>
+    <x:t>Damage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>풀 스윙</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어볼!!</x:t>
   </x:si>
   <x:si>
     <x:t>일단 휘두르기</x:t>
   </x:si>
   <x:si>
-    <x:t>풀 스윙</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어볼!!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>검기 날리기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_swing_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
+    <x:t>MotionPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_skill_explosion_01</x:t>
   </x:si>
   <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
+    <x:t>Icon/Icon_skill_swing_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/icon_skill_fireball_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>커피를 볶아 마신다. 모든 상태이상이 해제된다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_rest_coffee_01</x:t>
   </x:si>
   <x:si>
     <x:t>skill_normalSword_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_rest_coffee_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/icon_skill_fireball_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_skill_swing_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>커피를 볶아 마신다. 모든 상태이상이 해제된다.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -235,7 +247,10 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="17">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -891,396 +906,427 @@
   <x:dimension ref="A1:O35"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
-    <x:col min="1" max="1" width="23" style="2" customWidth="1"/>
-    <x:col min="2" max="2" width="19.5703125" style="2" customWidth="1"/>
-    <x:col min="3" max="3" width="50.7109375" style="2" customWidth="1"/>
-    <x:col min="4" max="4" width="28.5703125" style="1" customWidth="1"/>
-    <x:col min="5" max="5" width="30.5703125" style="2" customWidth="1"/>
+    <x:col min="1" max="1" width="23" style="3" customWidth="1"/>
+    <x:col min="2" max="2" width="19.5703125" style="3" customWidth="1"/>
+    <x:col min="3" max="3" width="50.7109375" style="3" customWidth="1"/>
+    <x:col min="4" max="4" width="28.5703125" style="2" customWidth="1"/>
+    <x:col min="5" max="5" width="30.5703125" style="3" customWidth="1"/>
+    <x:col min="6" max="7" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A1" s="3" t="s">
+      <x:c r="A1" s="4" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B1" s="4"/>
+      <x:c r="C1" s="4"/>
+    </x:row>
+    <x:row r="2" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A2" s="4" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B2" s="4" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C2" s="4" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E2" s="3" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A3" s="5" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B3" s="5" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C3" s="5" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F3" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G3" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A4" s="7" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="7" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E4" s="6"/>
+      <x:c r="F4" s="6"/>
+      <x:c r="G4" s="6"/>
+      <x:c r="H4" s="6"/>
+      <x:c r="I4" s="6"/>
+      <x:c r="J4" s="6"/>
+      <x:c r="K4" s="6"/>
+      <x:c r="L4" s="6"/>
+      <x:c r="M4" s="6"/>
+      <x:c r="N4" s="6"/>
+      <x:c r="O4" s="6"/>
+    </x:row>
+    <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A5" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B5" s="8" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C5" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E5" s="6"/>
+      <x:c r="F5" s="6"/>
+      <x:c r="G5" s="6"/>
+      <x:c r="H5" s="6"/>
+      <x:c r="I5" s="6"/>
+      <x:c r="J5" s="6"/>
+      <x:c r="K5" s="6"/>
+      <x:c r="L5" s="6"/>
+      <x:c r="M5" s="6"/>
+      <x:c r="N5" s="6"/>
+      <x:c r="O5" s="6"/>
+    </x:row>
+    <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A6" s="8" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B6" s="8" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C6" s="8" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E6" s="6"/>
+      <x:c r="F6" s="6"/>
+      <x:c r="G6" s="6"/>
+      <x:c r="H6" s="6"/>
+      <x:c r="I6" s="6"/>
+      <x:c r="J6" s="6"/>
+      <x:c r="K6" s="6"/>
+      <x:c r="L6" s="6"/>
+      <x:c r="M6" s="6"/>
+      <x:c r="N6" s="6"/>
+      <x:c r="O6" s="6"/>
+    </x:row>
+    <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A7" s="15" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B7" s="15" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C7" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B1" s="3"/>
-      <x:c r="C1" s="3"/>
-    </x:row>
-    <x:row r="2" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A2" s="3" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B2" s="3" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C2" s="3" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A3" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B3" s="4" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C3" s="4" t="s">
+      <x:c r="D7" s="16" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E7" s="6"/>
+      <x:c r="F7" s="6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G7" s="6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H7" s="6"/>
+      <x:c r="I7" s="6"/>
+      <x:c r="J7" s="6"/>
+      <x:c r="K7" s="6"/>
+      <x:c r="L7" s="6"/>
+      <x:c r="M7" s="6"/>
+      <x:c r="N7" s="6"/>
+      <x:c r="O7" s="6"/>
+    </x:row>
+    <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A8" s="15" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A4" s="6" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B4" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C4" s="6" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E4" s="5"/>
-      <x:c r="F4" s="5"/>
-      <x:c r="G4" s="5"/>
-      <x:c r="H4" s="5"/>
-      <x:c r="I4" s="5"/>
-      <x:c r="J4" s="5"/>
-      <x:c r="K4" s="5"/>
-      <x:c r="L4" s="5"/>
-      <x:c r="M4" s="5"/>
-      <x:c r="N4" s="5"/>
-      <x:c r="O4" s="5"/>
-    </x:row>
-    <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A5" s="6" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B5" s="7" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C5" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E5" s="5"/>
-      <x:c r="F5" s="5"/>
-      <x:c r="G5" s="5"/>
-      <x:c r="H5" s="5"/>
-      <x:c r="I5" s="5"/>
-      <x:c r="J5" s="5"/>
-      <x:c r="K5" s="5"/>
-      <x:c r="L5" s="5"/>
-      <x:c r="M5" s="5"/>
-      <x:c r="N5" s="5"/>
-      <x:c r="O5" s="5"/>
-    </x:row>
-    <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A6" s="7" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B6" s="7" t="s">
+      <x:c r="D8" s="16" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E8" s="6"/>
+      <x:c r="F8" s="6">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G8" s="6">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="6"/>
+      <x:c r="I8" s="6"/>
+      <x:c r="J8" s="6"/>
+      <x:c r="K8" s="6"/>
+      <x:c r="L8" s="6"/>
+      <x:c r="M8" s="6"/>
+      <x:c r="N8" s="6"/>
+      <x:c r="O8" s="6"/>
+    </x:row>
+    <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A9" s="15" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C6" s="7" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E6" s="5"/>
-      <x:c r="F6" s="5"/>
-      <x:c r="G6" s="5"/>
-      <x:c r="H6" s="5"/>
-      <x:c r="I6" s="5"/>
-      <x:c r="J6" s="5"/>
-      <x:c r="K6" s="5"/>
-      <x:c r="L6" s="5"/>
-      <x:c r="M6" s="5"/>
-      <x:c r="N6" s="5"/>
-      <x:c r="O6" s="5"/>
-    </x:row>
-    <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A7" s="14" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B7" s="14" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="B9" s="15" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D7" s="15" t="s">
+      <x:c r="C9" s="15" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="E7" s="5"/>
-      <x:c r="F7" s="5"/>
-      <x:c r="G7" s="5"/>
-      <x:c r="H7" s="5"/>
-      <x:c r="I7" s="5"/>
-      <x:c r="J7" s="5"/>
-      <x:c r="K7" s="5"/>
-      <x:c r="L7" s="5"/>
-      <x:c r="M7" s="5"/>
-      <x:c r="N7" s="5"/>
-      <x:c r="O7" s="5"/>
-    </x:row>
-    <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A8" s="14" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B8" s="14" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E8" s="5"/>
-      <x:c r="F8" s="5"/>
-      <x:c r="G8" s="5"/>
-      <x:c r="H8" s="5"/>
-      <x:c r="I8" s="5"/>
-      <x:c r="J8" s="5"/>
-      <x:c r="K8" s="5"/>
-      <x:c r="L8" s="5"/>
-      <x:c r="M8" s="5"/>
-      <x:c r="N8" s="5"/>
-      <x:c r="O8" s="5"/>
-    </x:row>
-    <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A9" s="14" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B9" s="14" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E9" s="5"/>
-      <x:c r="F9" s="5"/>
-      <x:c r="G9" s="5"/>
-      <x:c r="H9" s="5"/>
-      <x:c r="I9" s="5"/>
-      <x:c r="J9" s="5"/>
-      <x:c r="K9" s="5"/>
-      <x:c r="L9" s="5"/>
-      <x:c r="M9" s="5"/>
-      <x:c r="N9" s="5"/>
-      <x:c r="O9" s="5"/>
+      <x:c r="E9" s="6"/>
+      <x:c r="F9" s="6">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G9" s="6">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H9" s="6"/>
+      <x:c r="I9" s="6"/>
+      <x:c r="J9" s="6"/>
+      <x:c r="K9" s="6"/>
+      <x:c r="L9" s="6"/>
+      <x:c r="M9" s="6"/>
+      <x:c r="N9" s="6"/>
+      <x:c r="O9" s="6"/>
     </x:row>
     <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A10" s="9"/>
-      <x:c r="B10" s="9"/>
-      <x:c r="C10" s="9"/>
-      <x:c r="D10" s="5"/>
-      <x:c r="E10" s="5"/>
-      <x:c r="F10" s="5"/>
-      <x:c r="G10" s="5"/>
-      <x:c r="H10" s="5"/>
-      <x:c r="I10" s="5"/>
-      <x:c r="J10" s="5"/>
-      <x:c r="K10" s="5"/>
-      <x:c r="L10" s="5"/>
-      <x:c r="M10" s="5"/>
-      <x:c r="N10" s="5"/>
-      <x:c r="O10" s="5"/>
+      <x:c r="A10" s="10"/>
+      <x:c r="B10" s="10"/>
+      <x:c r="C10" s="10"/>
+      <x:c r="D10" s="6"/>
+      <x:c r="E10" s="6"/>
+      <x:c r="F10" s="6"/>
+      <x:c r="G10" s="6"/>
+      <x:c r="H10" s="6"/>
+      <x:c r="I10" s="6"/>
+      <x:c r="J10" s="6"/>
+      <x:c r="K10" s="6"/>
+      <x:c r="L10" s="6"/>
+      <x:c r="M10" s="6"/>
+      <x:c r="N10" s="6"/>
+      <x:c r="O10" s="6"/>
     </x:row>
     <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A11" s="9"/>
-      <x:c r="B11" s="9"/>
-      <x:c r="C11" s="9"/>
-      <x:c r="D11" s="5"/>
-      <x:c r="E11" s="5"/>
-      <x:c r="F11" s="5"/>
-      <x:c r="G11" s="5"/>
-      <x:c r="H11" s="5"/>
-      <x:c r="I11" s="5"/>
-      <x:c r="J11" s="5"/>
-      <x:c r="K11" s="5"/>
-      <x:c r="L11" s="5"/>
-      <x:c r="M11" s="5"/>
-      <x:c r="N11" s="5"/>
-      <x:c r="O11" s="5"/>
+      <x:c r="A11" s="10"/>
+      <x:c r="B11" s="10"/>
+      <x:c r="C11" s="10"/>
+      <x:c r="D11" s="6"/>
+      <x:c r="E11" s="6"/>
+      <x:c r="F11" s="6"/>
+      <x:c r="G11" s="6"/>
+      <x:c r="H11" s="6"/>
+      <x:c r="I11" s="6"/>
+      <x:c r="J11" s="6"/>
+      <x:c r="K11" s="6"/>
+      <x:c r="L11" s="6"/>
+      <x:c r="M11" s="6"/>
+      <x:c r="N11" s="6"/>
+      <x:c r="O11" s="6"/>
     </x:row>
     <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A12" s="8"/>
-      <x:c r="B12" s="8"/>
-      <x:c r="C12" s="8"/>
-      <x:c r="D12" s="5"/>
-      <x:c r="E12" s="5"/>
-      <x:c r="F12" s="5"/>
-      <x:c r="G12" s="5"/>
-      <x:c r="H12" s="5"/>
-      <x:c r="I12" s="5"/>
-      <x:c r="J12" s="5"/>
-      <x:c r="K12" s="5"/>
-      <x:c r="L12" s="5"/>
-      <x:c r="M12" s="5"/>
-      <x:c r="N12" s="5"/>
-      <x:c r="O12" s="5"/>
+      <x:c r="A12" s="9"/>
+      <x:c r="B12" s="9"/>
+      <x:c r="C12" s="9"/>
+      <x:c r="D12" s="6"/>
+      <x:c r="E12" s="6"/>
+      <x:c r="F12" s="6"/>
+      <x:c r="G12" s="6"/>
+      <x:c r="H12" s="6"/>
+      <x:c r="I12" s="6"/>
+      <x:c r="J12" s="6"/>
+      <x:c r="K12" s="6"/>
+      <x:c r="L12" s="6"/>
+      <x:c r="M12" s="6"/>
+      <x:c r="N12" s="6"/>
+      <x:c r="O12" s="6"/>
     </x:row>
     <x:row r="13" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A13" s="6"/>
-      <x:c r="B13" s="6"/>
-      <x:c r="C13" s="6"/>
-      <x:c r="D13" s="5"/>
-      <x:c r="E13" s="5"/>
-      <x:c r="F13" s="5"/>
-      <x:c r="G13" s="5"/>
-      <x:c r="H13" s="5"/>
-      <x:c r="I13" s="5"/>
-      <x:c r="J13" s="5"/>
-      <x:c r="K13" s="5"/>
-      <x:c r="L13" s="5"/>
-      <x:c r="M13" s="5"/>
-      <x:c r="N13" s="5"/>
-      <x:c r="O13" s="5"/>
+      <x:c r="A13" s="7"/>
+      <x:c r="B13" s="7"/>
+      <x:c r="C13" s="7"/>
+      <x:c r="D13" s="6"/>
+      <x:c r="E13" s="6"/>
+      <x:c r="F13" s="6"/>
+      <x:c r="G13" s="6"/>
+      <x:c r="H13" s="6"/>
+      <x:c r="I13" s="6"/>
+      <x:c r="J13" s="6"/>
+      <x:c r="K13" s="6"/>
+      <x:c r="L13" s="6"/>
+      <x:c r="M13" s="6"/>
+      <x:c r="N13" s="6"/>
+      <x:c r="O13" s="6"/>
     </x:row>
     <x:row r="14" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A14" s="9"/>
-      <x:c r="B14" s="9"/>
-      <x:c r="C14" s="9"/>
-      <x:c r="D14" s="5"/>
-      <x:c r="E14" s="5"/>
-      <x:c r="F14" s="5"/>
-      <x:c r="G14" s="5"/>
-      <x:c r="H14" s="5"/>
-      <x:c r="I14" s="5"/>
-      <x:c r="J14" s="5"/>
-      <x:c r="K14" s="5"/>
-      <x:c r="L14" s="5"/>
-      <x:c r="M14" s="5"/>
-      <x:c r="N14" s="5"/>
-      <x:c r="O14" s="5"/>
+      <x:c r="A14" s="10"/>
+      <x:c r="B14" s="10"/>
+      <x:c r="C14" s="10"/>
+      <x:c r="D14" s="6"/>
+      <x:c r="E14" s="6"/>
+      <x:c r="F14" s="6"/>
+      <x:c r="G14" s="6"/>
+      <x:c r="H14" s="6"/>
+      <x:c r="I14" s="6"/>
+      <x:c r="J14" s="6"/>
+      <x:c r="K14" s="6"/>
+      <x:c r="L14" s="6"/>
+      <x:c r="M14" s="6"/>
+      <x:c r="N14" s="6"/>
+      <x:c r="O14" s="6"/>
     </x:row>
     <x:row r="15" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A15" s="9"/>
-      <x:c r="B15" s="9"/>
-      <x:c r="C15" s="9"/>
-      <x:c r="D15" s="5"/>
-      <x:c r="E15" s="5"/>
-      <x:c r="F15" s="5"/>
-      <x:c r="G15" s="5"/>
-      <x:c r="H15" s="5"/>
-      <x:c r="I15" s="5"/>
-      <x:c r="J15" s="5"/>
-      <x:c r="K15" s="5"/>
-      <x:c r="L15" s="5"/>
-      <x:c r="M15" s="5"/>
-      <x:c r="N15" s="5"/>
-      <x:c r="O15" s="5"/>
+      <x:c r="A15" s="10"/>
+      <x:c r="B15" s="10"/>
+      <x:c r="C15" s="10"/>
+      <x:c r="D15" s="6"/>
+      <x:c r="E15" s="6"/>
+      <x:c r="F15" s="6"/>
+      <x:c r="G15" s="6"/>
+      <x:c r="H15" s="6"/>
+      <x:c r="I15" s="6"/>
+      <x:c r="J15" s="6"/>
+      <x:c r="K15" s="6"/>
+      <x:c r="L15" s="6"/>
+      <x:c r="M15" s="6"/>
+      <x:c r="N15" s="6"/>
+      <x:c r="O15" s="6"/>
     </x:row>
     <x:row r="16" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A16" s="10"/>
-      <x:c r="B16" s="10"/>
-      <x:c r="C16" s="10"/>
+      <x:c r="A16" s="11"/>
+      <x:c r="B16" s="11"/>
+      <x:c r="C16" s="11"/>
     </x:row>
     <x:row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A17" s="11"/>
-      <x:c r="B17" s="11"/>
-      <x:c r="C17" s="11"/>
+      <x:c r="A17" s="12"/>
+      <x:c r="B17" s="12"/>
+      <x:c r="C17" s="12"/>
     </x:row>
     <x:row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A18" s="11"/>
-      <x:c r="B18" s="11"/>
-      <x:c r="C18" s="11"/>
+      <x:c r="A18" s="12"/>
+      <x:c r="B18" s="12"/>
+      <x:c r="C18" s="12"/>
     </x:row>
     <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A19" s="11"/>
-      <x:c r="B19" s="11"/>
-      <x:c r="C19" s="11"/>
-      <x:c r="D19" s="5"/>
-      <x:c r="E19" s="5"/>
+      <x:c r="A19" s="12"/>
+      <x:c r="B19" s="12"/>
+      <x:c r="C19" s="12"/>
+      <x:c r="D19" s="6"/>
+      <x:c r="E19" s="6"/>
     </x:row>
     <x:row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A20" s="11"/>
-      <x:c r="B20" s="11"/>
-      <x:c r="C20" s="11"/>
+      <x:c r="A20" s="12"/>
+      <x:c r="B20" s="12"/>
+      <x:c r="C20" s="12"/>
     </x:row>
     <x:row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A21" s="11"/>
-      <x:c r="B21" s="11"/>
-      <x:c r="C21" s="11"/>
+      <x:c r="A21" s="12"/>
+      <x:c r="B21" s="12"/>
+      <x:c r="C21" s="12"/>
     </x:row>
     <x:row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A22" s="11"/>
-      <x:c r="B22" s="11"/>
-      <x:c r="C22" s="11"/>
+      <x:c r="A22" s="12"/>
+      <x:c r="B22" s="12"/>
+      <x:c r="C22" s="12"/>
     </x:row>
     <x:row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A23" s="11"/>
-      <x:c r="B23" s="11"/>
-      <x:c r="C23" s="11"/>
+      <x:c r="A23" s="12"/>
+      <x:c r="B23" s="12"/>
+      <x:c r="C23" s="12"/>
     </x:row>
     <x:row r="24" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A24" s="11"/>
-      <x:c r="B24" s="11"/>
-      <x:c r="C24" s="11"/>
+      <x:c r="A24" s="12"/>
+      <x:c r="B24" s="12"/>
+      <x:c r="C24" s="12"/>
     </x:row>
     <x:row r="25" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A25" s="11"/>
-      <x:c r="B25" s="11"/>
-      <x:c r="C25" s="11"/>
-      <x:c r="E25" s="5"/>
+      <x:c r="A25" s="12"/>
+      <x:c r="B25" s="12"/>
+      <x:c r="C25" s="12"/>
+      <x:c r="E25" s="6"/>
     </x:row>
     <x:row r="26" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A26" s="12"/>
-      <x:c r="B26" s="12"/>
-      <x:c r="C26" s="12"/>
-      <x:c r="E26" s="5"/>
+      <x:c r="A26" s="13"/>
+      <x:c r="B26" s="13"/>
+      <x:c r="C26" s="13"/>
+      <x:c r="E26" s="6"/>
     </x:row>
     <x:row r="27" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A27" s="12"/>
-      <x:c r="B27" s="12"/>
-      <x:c r="C27" s="12"/>
-      <x:c r="E27" s="5"/>
+      <x:c r="A27" s="13"/>
+      <x:c r="B27" s="13"/>
+      <x:c r="C27" s="13"/>
+      <x:c r="E27" s="6"/>
     </x:row>
     <x:row r="28" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A28" s="12"/>
-      <x:c r="B28" s="12"/>
-      <x:c r="C28" s="12"/>
-      <x:c r="E28" s="5"/>
+      <x:c r="A28" s="13"/>
+      <x:c r="B28" s="13"/>
+      <x:c r="C28" s="13"/>
+      <x:c r="E28" s="6"/>
     </x:row>
     <x:row r="29" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A29" s="12"/>
-      <x:c r="B29" s="12"/>
-      <x:c r="C29" s="12"/>
+      <x:c r="A29" s="13"/>
+      <x:c r="B29" s="13"/>
+      <x:c r="C29" s="13"/>
     </x:row>
     <x:row r="30" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A30" s="12"/>
-      <x:c r="B30" s="12"/>
-      <x:c r="C30" s="12"/>
+      <x:c r="A30" s="13"/>
+      <x:c r="B30" s="13"/>
+      <x:c r="C30" s="13"/>
     </x:row>
     <x:row r="31" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A31" s="12"/>
-      <x:c r="B31" s="12"/>
-      <x:c r="C31" s="12"/>
+      <x:c r="A31" s="13"/>
+      <x:c r="B31" s="13"/>
+      <x:c r="C31" s="13"/>
     </x:row>
     <x:row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A32" s="13"/>
-      <x:c r="B32" s="13"/>
-      <x:c r="C32" s="13"/>
+      <x:c r="A32" s="14"/>
+      <x:c r="B32" s="14"/>
+      <x:c r="C32" s="14"/>
     </x:row>
     <x:row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A33" s="13"/>
-      <x:c r="B33" s="13"/>
-      <x:c r="C33" s="13"/>
+      <x:c r="A33" s="14"/>
+      <x:c r="B33" s="14"/>
+      <x:c r="C33" s="14"/>
     </x:row>
     <x:row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A34" s="13"/>
-      <x:c r="B34" s="13"/>
-      <x:c r="C34" s="13"/>
+      <x:c r="A34" s="14"/>
+      <x:c r="B34" s="14"/>
+      <x:c r="C34" s="14"/>
     </x:row>
     <x:row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A35" s="13"/>
-      <x:c r="B35" s="13"/>
-      <x:c r="C35" s="13"/>
+      <x:c r="A35" s="14"/>
+      <x:c r="B35" s="14"/>
+      <x:c r="C35" s="14"/>
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1"/>
     <x:row r="37" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -19,84 +19,135 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="46">
+  <x:si>
+    <x:t>Icon/icon_skill_fireball_02_special</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_skill_swing_01_special</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_normalSword_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_swing_01_special</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_rest_coffee_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>특 급 대 폭 발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필살 파이어볼!!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MotionPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필살 익스플로젼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_skill_explosion_01_special</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_skill_explosion_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어볼!!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>익스플로젼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>커피 마시기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>풀 스윙</x:t>
+  </x:si>
+  <x:si>
+    <x:t>검기 날리기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대 폭 발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Damage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필살 휘두르기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필살 풀 스윙</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Special</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일단 휘두르기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필살 파이어볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
   <x:si>
     <x:t>CostMp</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
+    <x:t>불로 된 구체를 만들어 날린다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_fireball_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_explosion_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적을 벨 수 있는 검기를 날린다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_fireball_02</x:t>
   </x:si>
   <x:si>
     <x:t>skill_swing_01</x:t>
   </x:si>
   <x:si>
-    <x:t>적을 벨 수 있는 검기를 날린다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_fireball_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불로 된 구체를 만들어 날린다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_fireball_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_explosion_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대 폭 발</x:t>
-  </x:si>
-  <x:si>
-    <x:t>익스플로젼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>검기 날리기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>커피 마시기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Damage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>풀 스윙</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어볼!!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일단 휘두르기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MotionPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_skill_explosion_01</x:t>
+    <x:t>skill_explosion_01_special</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_fireball_02_special</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_skill_swing_01</x:t>
@@ -106,19 +157,13 @@
   </x:si>
   <x:si>
     <x:t>커피를 볶아 마신다. 모든 상태이상이 해제된다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_rest_coffee_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_normalSword_01</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="8">
+  <x:fonts count="7">
     <x:font>
       <x:name val="Arial"/>
       <x:sz val="10"/>
@@ -150,12 +195,7 @@
       <x:color rgb="ff000000"/>
     </x:font>
     <x:font>
-      <x:name val="&quot;맑은 고딕&quot;"/>
-      <x:sz val="10"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="&quot;맑은 고딕&quot;"/>
+      <x:name val="Arial"/>
       <x:sz val="11"/>
       <x:color rgb="ff008000"/>
     </x:font>
@@ -166,18 +206,6 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="ffc6efce"/>
-        <x:bgColor rgb="ffc6efce"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="ffffffff"/>
-        <x:bgColor rgb="ff4d93d9"/>
-      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -194,7 +222,19 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="ffffffff"/>
+        <x:bgColor rgb="ff4d93d9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="ffffffff"/>
         <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="ffc6efce"/>
+        <x:bgColor rgb="ffc6efce"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -260,44 +300,44 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
+      <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
+      <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
+      <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -909,424 +949,609 @@
     <x:col min="1" max="1" width="23" style="3" customWidth="1"/>
     <x:col min="2" max="2" width="19.5703125" style="3" customWidth="1"/>
     <x:col min="3" max="3" width="50.7109375" style="3" customWidth="1"/>
-    <x:col min="4" max="4" width="28.5703125" style="2" customWidth="1"/>
+    <x:col min="4" max="4" width="35.85546875" style="2" customWidth="1"/>
     <x:col min="5" max="5" width="30.5703125" style="3" customWidth="1"/>
     <x:col min="6" max="7" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A1" s="4" t="s">
+    <x:row r="1" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A1" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B1" s="10"/>
+      <x:c r="C1" s="10"/>
+      <x:c r="D1" s="11"/>
+      <x:c r="E1" s="4"/>
+      <x:c r="F1" s="11"/>
+      <x:c r="G1" s="11"/>
+      <x:c r="H1" s="11"/>
+      <x:c r="I1" s="11"/>
+      <x:c r="J1" s="11"/>
+      <x:c r="K1" s="11"/>
+    </x:row>
+    <x:row r="2" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A2" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B2" s="10" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C2" s="10" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D2" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E2" s="4" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F2" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G2" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H2" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I2" s="11"/>
+      <x:c r="J2" s="11"/>
+      <x:c r="K2" s="11"/>
+    </x:row>
+    <x:row r="3" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A3" s="12" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B3" s="12" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D3" s="11" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E3" s="4" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F3" s="11" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G3" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H3" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I3" s="11"/>
+      <x:c r="J3" s="11"/>
+      <x:c r="K3" s="11"/>
+    </x:row>
+    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A4" s="13" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B4" s="13" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C4" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D4" s="11"/>
+      <x:c r="E4" s="4"/>
+      <x:c r="F4" s="4"/>
+      <x:c r="G4" s="4"/>
+      <x:c r="H4" s="4"/>
+      <x:c r="I4" s="4"/>
+      <x:c r="J4" s="4"/>
+      <x:c r="K4" s="4"/>
+      <x:c r="L4" s="4"/>
+      <x:c r="M4" s="4"/>
+      <x:c r="N4" s="4"/>
+      <x:c r="O4" s="4"/>
+    </x:row>
+    <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A5" s="13" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B5" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-    </x:row>
-    <x:row r="2" spans="1:7" ht="15.75" customHeight="1">
-      <x:c r="A2" s="4" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B2" s="4" t="s">
+      <x:c r="C5" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D5" s="11"/>
+      <x:c r="E5" s="4"/>
+      <x:c r="F5" s="4"/>
+      <x:c r="G5" s="4"/>
+      <x:c r="H5" s="4"/>
+      <x:c r="I5" s="4"/>
+      <x:c r="J5" s="4"/>
+      <x:c r="K5" s="4"/>
+      <x:c r="L5" s="4"/>
+      <x:c r="M5" s="4"/>
+      <x:c r="N5" s="4"/>
+      <x:c r="O5" s="4"/>
+    </x:row>
+    <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A6" s="14" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D6" s="11"/>
+      <x:c r="E6" s="4"/>
+      <x:c r="F6" s="4"/>
+      <x:c r="G6" s="4"/>
+      <x:c r="H6" s="4"/>
+      <x:c r="I6" s="4"/>
+      <x:c r="J6" s="4"/>
+      <x:c r="K6" s="4"/>
+      <x:c r="L6" s="4"/>
+      <x:c r="M6" s="4"/>
+      <x:c r="N6" s="4"/>
+      <x:c r="O6" s="4"/>
+    </x:row>
+    <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A7" s="8" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B7" s="8" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C7" s="8" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D7" s="9" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E7" s="4"/>
+      <x:c r="F7" s="4">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G7" s="4">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H7" s="4" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="I7" s="4"/>
+      <x:c r="J7" s="4"/>
+      <x:c r="K7" s="4"/>
+      <x:c r="L7" s="4"/>
+      <x:c r="M7" s="4"/>
+      <x:c r="N7" s="4"/>
+      <x:c r="O7" s="4"/>
+    </x:row>
+    <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A8" s="8" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B8" s="8" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C8" s="8" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E8" s="4"/>
+      <x:c r="F8" s="4">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G8" s="4">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="4" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="I8" s="4"/>
+      <x:c r="J8" s="4"/>
+      <x:c r="K8" s="4"/>
+      <x:c r="L8" s="4"/>
+      <x:c r="M8" s="4"/>
+      <x:c r="N8" s="4"/>
+      <x:c r="O8" s="4"/>
+    </x:row>
+    <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A9" s="8" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B9" s="8" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C9" s="8" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D9" s="9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C2" s="4" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D2" s="2" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E2" s="3" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7" ht="15.75" customHeight="1">
-      <x:c r="A3" s="5" t="s">
+      <x:c r="E9" s="4"/>
+      <x:c r="F9" s="4">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G9" s="4">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H9" s="4" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="I9" s="4"/>
+      <x:c r="J9" s="4"/>
+      <x:c r="K9" s="4"/>
+      <x:c r="L9" s="4"/>
+      <x:c r="M9" s="4"/>
+      <x:c r="N9" s="4"/>
+      <x:c r="O9" s="4"/>
+    </x:row>
+    <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A10" s="15" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B10" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D10" s="9" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B3" s="5" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C3" s="5" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D3" s="2" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E3" s="3" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G3" s="1" t="s">
+      <x:c r="E10" s="4"/>
+      <x:c r="F10" s="4">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G10" s="4">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H10" s="4" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I10" s="4"/>
+      <x:c r="J10" s="4"/>
+      <x:c r="K10" s="4"/>
+      <x:c r="L10" s="4"/>
+      <x:c r="M10" s="4"/>
+      <x:c r="N10" s="4"/>
+      <x:c r="O10" s="4"/>
+    </x:row>
+    <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A11" s="8" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B11" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D11" s="9" t="s">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A4" s="7" t="s">
+      <x:c r="E11" s="4"/>
+      <x:c r="F11" s="4">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G11" s="4">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H11" s="4" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I11" s="4"/>
+      <x:c r="J11" s="4"/>
+      <x:c r="K11" s="4"/>
+      <x:c r="L11" s="4"/>
+      <x:c r="M11" s="4"/>
+      <x:c r="N11" s="4"/>
+      <x:c r="O11" s="4"/>
+    </x:row>
+    <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A12" s="8" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B12" s="16" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C12" s="16" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B4" s="7" t="s">
+      <x:c r="D12" s="9" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C4" s="7" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E4" s="6"/>
-      <x:c r="F4" s="6"/>
-      <x:c r="G4" s="6"/>
-      <x:c r="H4" s="6"/>
-      <x:c r="I4" s="6"/>
-      <x:c r="J4" s="6"/>
-      <x:c r="K4" s="6"/>
-      <x:c r="L4" s="6"/>
-      <x:c r="M4" s="6"/>
-      <x:c r="N4" s="6"/>
-      <x:c r="O4" s="6"/>
-    </x:row>
-    <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A5" s="7" t="s">
+      <x:c r="E12" s="4"/>
+      <x:c r="F12" s="4">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G12" s="4">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H12" s="4" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B5" s="8" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C5" s="8" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E5" s="6"/>
-      <x:c r="F5" s="6"/>
-      <x:c r="G5" s="6"/>
-      <x:c r="H5" s="6"/>
-      <x:c r="I5" s="6"/>
-      <x:c r="J5" s="6"/>
-      <x:c r="K5" s="6"/>
-      <x:c r="L5" s="6"/>
-      <x:c r="M5" s="6"/>
-      <x:c r="N5" s="6"/>
-      <x:c r="O5" s="6"/>
-    </x:row>
-    <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A6" s="8" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B6" s="8" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C6" s="8" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E6" s="6"/>
-      <x:c r="F6" s="6"/>
-      <x:c r="G6" s="6"/>
-      <x:c r="H6" s="6"/>
-      <x:c r="I6" s="6"/>
-      <x:c r="J6" s="6"/>
-      <x:c r="K6" s="6"/>
-      <x:c r="L6" s="6"/>
-      <x:c r="M6" s="6"/>
-      <x:c r="N6" s="6"/>
-      <x:c r="O6" s="6"/>
-    </x:row>
-    <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A7" s="15" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B7" s="15" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C7" s="15" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D7" s="16" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E7" s="6"/>
-      <x:c r="F7" s="6">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G7" s="6">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H7" s="6"/>
-      <x:c r="I7" s="6"/>
-      <x:c r="J7" s="6"/>
-      <x:c r="K7" s="6"/>
-      <x:c r="L7" s="6"/>
-      <x:c r="M7" s="6"/>
-      <x:c r="N7" s="6"/>
-      <x:c r="O7" s="6"/>
-    </x:row>
-    <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A8" s="15" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B8" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D8" s="16" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E8" s="6"/>
-      <x:c r="F8" s="6">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G8" s="6">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="6"/>
-      <x:c r="I8" s="6"/>
-      <x:c r="J8" s="6"/>
-      <x:c r="K8" s="6"/>
-      <x:c r="L8" s="6"/>
-      <x:c r="M8" s="6"/>
-      <x:c r="N8" s="6"/>
-      <x:c r="O8" s="6"/>
-    </x:row>
-    <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A9" s="15" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B9" s="15" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D9" s="16" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E9" s="6"/>
-      <x:c r="F9" s="6">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G9" s="6">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H9" s="6"/>
-      <x:c r="I9" s="6"/>
-      <x:c r="J9" s="6"/>
-      <x:c r="K9" s="6"/>
-      <x:c r="L9" s="6"/>
-      <x:c r="M9" s="6"/>
-      <x:c r="N9" s="6"/>
-      <x:c r="O9" s="6"/>
-    </x:row>
-    <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A10" s="10"/>
-      <x:c r="B10" s="10"/>
-      <x:c r="C10" s="10"/>
-      <x:c r="D10" s="6"/>
-      <x:c r="E10" s="6"/>
-      <x:c r="F10" s="6"/>
-      <x:c r="G10" s="6"/>
-      <x:c r="H10" s="6"/>
-      <x:c r="I10" s="6"/>
-      <x:c r="J10" s="6"/>
-      <x:c r="K10" s="6"/>
-      <x:c r="L10" s="6"/>
-      <x:c r="M10" s="6"/>
-      <x:c r="N10" s="6"/>
-      <x:c r="O10" s="6"/>
-    </x:row>
-    <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A11" s="10"/>
-      <x:c r="B11" s="10"/>
-      <x:c r="C11" s="10"/>
-      <x:c r="D11" s="6"/>
-      <x:c r="E11" s="6"/>
-      <x:c r="F11" s="6"/>
-      <x:c r="G11" s="6"/>
-      <x:c r="H11" s="6"/>
-      <x:c r="I11" s="6"/>
-      <x:c r="J11" s="6"/>
-      <x:c r="K11" s="6"/>
-      <x:c r="L11" s="6"/>
-      <x:c r="M11" s="6"/>
-      <x:c r="N11" s="6"/>
-      <x:c r="O11" s="6"/>
-    </x:row>
-    <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A12" s="9"/>
-      <x:c r="B12" s="9"/>
-      <x:c r="C12" s="9"/>
-      <x:c r="D12" s="6"/>
-      <x:c r="E12" s="6"/>
-      <x:c r="F12" s="6"/>
-      <x:c r="G12" s="6"/>
-      <x:c r="H12" s="6"/>
-      <x:c r="I12" s="6"/>
-      <x:c r="J12" s="6"/>
-      <x:c r="K12" s="6"/>
-      <x:c r="L12" s="6"/>
-      <x:c r="M12" s="6"/>
-      <x:c r="N12" s="6"/>
-      <x:c r="O12" s="6"/>
+      <x:c r="I12" s="4"/>
+      <x:c r="J12" s="4"/>
+      <x:c r="K12" s="4"/>
+      <x:c r="L12" s="4"/>
+      <x:c r="M12" s="4"/>
+      <x:c r="N12" s="4"/>
+      <x:c r="O12" s="4"/>
     </x:row>
     <x:row r="13" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A13" s="7"/>
-      <x:c r="B13" s="7"/>
-      <x:c r="C13" s="7"/>
-      <x:c r="D13" s="6"/>
-      <x:c r="E13" s="6"/>
-      <x:c r="F13" s="6"/>
-      <x:c r="G13" s="6"/>
-      <x:c r="H13" s="6"/>
-      <x:c r="I13" s="6"/>
-      <x:c r="J13" s="6"/>
-      <x:c r="K13" s="6"/>
-      <x:c r="L13" s="6"/>
-      <x:c r="M13" s="6"/>
-      <x:c r="N13" s="6"/>
-      <x:c r="O13" s="6"/>
+      <x:c r="A13" s="13"/>
+      <x:c r="B13" s="13"/>
+      <x:c r="C13" s="13"/>
+      <x:c r="D13" s="4"/>
+      <x:c r="E13" s="4"/>
+      <x:c r="F13" s="4"/>
+      <x:c r="G13" s="4"/>
+      <x:c r="H13" s="4"/>
+      <x:c r="I13" s="4"/>
+      <x:c r="J13" s="4"/>
+      <x:c r="K13" s="4"/>
+      <x:c r="L13" s="4"/>
+      <x:c r="M13" s="4"/>
+      <x:c r="N13" s="4"/>
+      <x:c r="O13" s="4"/>
     </x:row>
     <x:row r="14" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A14" s="10"/>
-      <x:c r="B14" s="10"/>
-      <x:c r="C14" s="10"/>
-      <x:c r="D14" s="6"/>
-      <x:c r="E14" s="6"/>
-      <x:c r="F14" s="6"/>
-      <x:c r="G14" s="6"/>
-      <x:c r="H14" s="6"/>
-      <x:c r="I14" s="6"/>
-      <x:c r="J14" s="6"/>
-      <x:c r="K14" s="6"/>
-      <x:c r="L14" s="6"/>
-      <x:c r="M14" s="6"/>
-      <x:c r="N14" s="6"/>
-      <x:c r="O14" s="6"/>
+      <x:c r="A14" s="15"/>
+      <x:c r="B14" s="15"/>
+      <x:c r="C14" s="15"/>
+      <x:c r="D14" s="4"/>
+      <x:c r="E14" s="4"/>
+      <x:c r="F14" s="4"/>
+      <x:c r="G14" s="4"/>
+      <x:c r="H14" s="4"/>
+      <x:c r="I14" s="4"/>
+      <x:c r="J14" s="4"/>
+      <x:c r="K14" s="4"/>
+      <x:c r="L14" s="4"/>
+      <x:c r="M14" s="4"/>
+      <x:c r="N14" s="4"/>
+      <x:c r="O14" s="4"/>
     </x:row>
     <x:row r="15" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A15" s="10"/>
-      <x:c r="B15" s="10"/>
-      <x:c r="C15" s="10"/>
-      <x:c r="D15" s="6"/>
-      <x:c r="E15" s="6"/>
-      <x:c r="F15" s="6"/>
-      <x:c r="G15" s="6"/>
-      <x:c r="H15" s="6"/>
-      <x:c r="I15" s="6"/>
-      <x:c r="J15" s="6"/>
-      <x:c r="K15" s="6"/>
-      <x:c r="L15" s="6"/>
-      <x:c r="M15" s="6"/>
-      <x:c r="N15" s="6"/>
-      <x:c r="O15" s="6"/>
-    </x:row>
-    <x:row r="16" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A16" s="11"/>
-      <x:c r="B16" s="11"/>
-      <x:c r="C16" s="11"/>
-    </x:row>
-    <x:row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A17" s="12"/>
-      <x:c r="B17" s="12"/>
-      <x:c r="C17" s="12"/>
-    </x:row>
-    <x:row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A18" s="12"/>
-      <x:c r="B18" s="12"/>
-      <x:c r="C18" s="12"/>
-    </x:row>
-    <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A19" s="12"/>
-      <x:c r="B19" s="12"/>
-      <x:c r="C19" s="12"/>
-      <x:c r="D19" s="6"/>
-      <x:c r="E19" s="6"/>
-    </x:row>
-    <x:row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A20" s="12"/>
-      <x:c r="B20" s="12"/>
-      <x:c r="C20" s="12"/>
-    </x:row>
-    <x:row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A21" s="12"/>
-      <x:c r="B21" s="12"/>
-      <x:c r="C21" s="12"/>
-    </x:row>
-    <x:row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A22" s="12"/>
-      <x:c r="B22" s="12"/>
-      <x:c r="C22" s="12"/>
-    </x:row>
-    <x:row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A23" s="12"/>
-      <x:c r="B23" s="12"/>
-      <x:c r="C23" s="12"/>
-    </x:row>
-    <x:row r="24" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A24" s="12"/>
-      <x:c r="B24" s="12"/>
-      <x:c r="C24" s="12"/>
-    </x:row>
-    <x:row r="25" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A25" s="12"/>
-      <x:c r="B25" s="12"/>
-      <x:c r="C25" s="12"/>
-      <x:c r="E25" s="6"/>
-    </x:row>
-    <x:row r="26" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A26" s="13"/>
-      <x:c r="B26" s="13"/>
-      <x:c r="C26" s="13"/>
-      <x:c r="E26" s="6"/>
-    </x:row>
-    <x:row r="27" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A27" s="13"/>
-      <x:c r="B27" s="13"/>
-      <x:c r="C27" s="13"/>
-      <x:c r="E27" s="6"/>
-    </x:row>
-    <x:row r="28" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A28" s="13"/>
-      <x:c r="B28" s="13"/>
-      <x:c r="C28" s="13"/>
-      <x:c r="E28" s="6"/>
-    </x:row>
-    <x:row r="29" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A29" s="13"/>
-      <x:c r="B29" s="13"/>
-      <x:c r="C29" s="13"/>
-    </x:row>
-    <x:row r="30" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A30" s="13"/>
-      <x:c r="B30" s="13"/>
-      <x:c r="C30" s="13"/>
+      <x:c r="A15" s="15"/>
+      <x:c r="B15" s="15"/>
+      <x:c r="C15" s="15"/>
+      <x:c r="D15" s="4"/>
+      <x:c r="E15" s="4"/>
+      <x:c r="F15" s="4"/>
+      <x:c r="G15" s="4"/>
+      <x:c r="H15" s="4"/>
+      <x:c r="I15" s="4"/>
+      <x:c r="J15" s="4"/>
+      <x:c r="K15" s="4"/>
+      <x:c r="L15" s="4"/>
+      <x:c r="M15" s="4"/>
+      <x:c r="N15" s="4"/>
+      <x:c r="O15" s="4"/>
+    </x:row>
+    <x:row r="16" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A16" s="5"/>
+      <x:c r="B16" s="5"/>
+      <x:c r="C16" s="5"/>
+      <x:c r="D16" s="11"/>
+      <x:c r="E16" s="4"/>
+      <x:c r="F16" s="11"/>
+      <x:c r="G16" s="11"/>
+      <x:c r="H16" s="11"/>
+      <x:c r="I16" s="11"/>
+      <x:c r="J16" s="11"/>
+      <x:c r="K16" s="11"/>
+    </x:row>
+    <x:row r="17" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A17" s="5"/>
+      <x:c r="B17" s="5"/>
+      <x:c r="C17" s="5"/>
+      <x:c r="D17" s="11"/>
+      <x:c r="E17" s="4"/>
+      <x:c r="F17" s="11"/>
+      <x:c r="G17" s="11"/>
+      <x:c r="H17" s="11"/>
+      <x:c r="I17" s="11"/>
+      <x:c r="J17" s="11"/>
+      <x:c r="K17" s="11"/>
+    </x:row>
+    <x:row r="18" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A18" s="5"/>
+      <x:c r="B18" s="5"/>
+      <x:c r="C18" s="5"/>
+      <x:c r="D18" s="11"/>
+      <x:c r="E18" s="4"/>
+      <x:c r="F18" s="11"/>
+      <x:c r="G18" s="11"/>
+      <x:c r="H18" s="11"/>
+      <x:c r="I18" s="11"/>
+      <x:c r="J18" s="11"/>
+      <x:c r="K18" s="11"/>
+    </x:row>
+    <x:row r="19" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A19" s="5"/>
+      <x:c r="B19" s="5"/>
+      <x:c r="C19" s="5"/>
+      <x:c r="D19" s="4"/>
+      <x:c r="E19" s="4"/>
+      <x:c r="F19" s="11"/>
+      <x:c r="G19" s="11"/>
+      <x:c r="H19" s="11"/>
+      <x:c r="I19" s="11"/>
+      <x:c r="J19" s="11"/>
+      <x:c r="K19" s="11"/>
+    </x:row>
+    <x:row r="20" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A20" s="5"/>
+      <x:c r="B20" s="5"/>
+      <x:c r="C20" s="5"/>
+      <x:c r="D20" s="11"/>
+      <x:c r="E20" s="4"/>
+      <x:c r="F20" s="11"/>
+      <x:c r="G20" s="11"/>
+      <x:c r="H20" s="11"/>
+      <x:c r="I20" s="11"/>
+      <x:c r="J20" s="11"/>
+      <x:c r="K20" s="11"/>
+    </x:row>
+    <x:row r="21" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A21" s="5"/>
+      <x:c r="B21" s="5"/>
+      <x:c r="C21" s="5"/>
+      <x:c r="D21" s="11"/>
+      <x:c r="E21" s="4"/>
+      <x:c r="F21" s="11"/>
+      <x:c r="G21" s="11"/>
+      <x:c r="H21" s="11"/>
+      <x:c r="I21" s="11"/>
+      <x:c r="J21" s="11"/>
+      <x:c r="K21" s="11"/>
+    </x:row>
+    <x:row r="22" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A22" s="5"/>
+      <x:c r="B22" s="5"/>
+      <x:c r="C22" s="5"/>
+      <x:c r="D22" s="11"/>
+      <x:c r="E22" s="4"/>
+      <x:c r="F22" s="11"/>
+      <x:c r="G22" s="11"/>
+      <x:c r="H22" s="11"/>
+      <x:c r="I22" s="11"/>
+      <x:c r="J22" s="11"/>
+      <x:c r="K22" s="11"/>
+    </x:row>
+    <x:row r="23" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A23" s="5"/>
+      <x:c r="B23" s="5"/>
+      <x:c r="C23" s="5"/>
+      <x:c r="D23" s="11"/>
+      <x:c r="E23" s="4"/>
+      <x:c r="F23" s="11"/>
+      <x:c r="G23" s="11"/>
+      <x:c r="H23" s="11"/>
+      <x:c r="I23" s="11"/>
+      <x:c r="J23" s="11"/>
+      <x:c r="K23" s="11"/>
+    </x:row>
+    <x:row r="24" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A24" s="5"/>
+      <x:c r="B24" s="5"/>
+      <x:c r="C24" s="5"/>
+      <x:c r="D24" s="11"/>
+      <x:c r="E24" s="4"/>
+      <x:c r="F24" s="11"/>
+      <x:c r="G24" s="11"/>
+      <x:c r="H24" s="11"/>
+      <x:c r="I24" s="11"/>
+      <x:c r="J24" s="11"/>
+      <x:c r="K24" s="11"/>
+    </x:row>
+    <x:row r="25" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A25" s="5"/>
+      <x:c r="B25" s="5"/>
+      <x:c r="C25" s="5"/>
+      <x:c r="D25" s="11"/>
+      <x:c r="E25" s="4"/>
+      <x:c r="F25" s="11"/>
+      <x:c r="G25" s="11"/>
+      <x:c r="H25" s="11"/>
+      <x:c r="I25" s="11"/>
+      <x:c r="J25" s="11"/>
+      <x:c r="K25" s="11"/>
+    </x:row>
+    <x:row r="26" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A26" s="6"/>
+      <x:c r="B26" s="6"/>
+      <x:c r="C26" s="6"/>
+      <x:c r="D26" s="11"/>
+      <x:c r="E26" s="4"/>
+      <x:c r="F26" s="11"/>
+      <x:c r="G26" s="11"/>
+      <x:c r="H26" s="11"/>
+      <x:c r="I26" s="11"/>
+      <x:c r="J26" s="11"/>
+      <x:c r="K26" s="11"/>
+    </x:row>
+    <x:row r="27" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A27" s="6"/>
+      <x:c r="B27" s="6"/>
+      <x:c r="C27" s="6"/>
+      <x:c r="D27" s="11"/>
+      <x:c r="E27" s="4"/>
+      <x:c r="F27" s="11"/>
+      <x:c r="G27" s="11"/>
+      <x:c r="H27" s="11"/>
+      <x:c r="I27" s="11"/>
+      <x:c r="J27" s="11"/>
+      <x:c r="K27" s="11"/>
+    </x:row>
+    <x:row r="28" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A28" s="6"/>
+      <x:c r="B28" s="6"/>
+      <x:c r="C28" s="6"/>
+      <x:c r="D28" s="11"/>
+      <x:c r="E28" s="4"/>
+      <x:c r="F28" s="11"/>
+      <x:c r="G28" s="11"/>
+      <x:c r="H28" s="11"/>
+      <x:c r="I28" s="11"/>
+      <x:c r="J28" s="11"/>
+      <x:c r="K28" s="11"/>
+    </x:row>
+    <x:row r="29" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A29" s="6"/>
+      <x:c r="B29" s="6"/>
+      <x:c r="C29" s="6"/>
+      <x:c r="D29" s="11"/>
+      <x:c r="E29" s="4"/>
+      <x:c r="F29" s="11"/>
+      <x:c r="G29" s="11"/>
+      <x:c r="H29" s="11"/>
+      <x:c r="I29" s="11"/>
+      <x:c r="J29" s="11"/>
+      <x:c r="K29" s="11"/>
+    </x:row>
+    <x:row r="30" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A30" s="6"/>
+      <x:c r="B30" s="6"/>
+      <x:c r="C30" s="6"/>
+      <x:c r="D30" s="11"/>
+      <x:c r="E30" s="4"/>
+      <x:c r="F30" s="11"/>
+      <x:c r="G30" s="11"/>
+      <x:c r="H30" s="11"/>
+      <x:c r="I30" s="11"/>
+      <x:c r="J30" s="11"/>
+      <x:c r="K30" s="11"/>
     </x:row>
     <x:row r="31" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A31" s="13"/>
-      <x:c r="B31" s="13"/>
-      <x:c r="C31" s="13"/>
+      <x:c r="A31" s="6"/>
+      <x:c r="B31" s="6"/>
+      <x:c r="C31" s="6"/>
     </x:row>
     <x:row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A32" s="14"/>
-      <x:c r="B32" s="14"/>
-      <x:c r="C32" s="14"/>
+      <x:c r="A32" s="7"/>
+      <x:c r="B32" s="7"/>
+      <x:c r="C32" s="7"/>
     </x:row>
     <x:row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A33" s="14"/>
-      <x:c r="B33" s="14"/>
-      <x:c r="C33" s="14"/>
+      <x:c r="A33" s="7"/>
+      <x:c r="B33" s="7"/>
+      <x:c r="C33" s="7"/>
     </x:row>
     <x:row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A34" s="14"/>
-      <x:c r="B34" s="14"/>
-      <x:c r="C34" s="14"/>
+      <x:c r="A34" s="7"/>
+      <x:c r="B34" s="7"/>
+      <x:c r="C34" s="7"/>
     </x:row>
     <x:row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A35" s="14"/>
-      <x:c r="B35" s="14"/>
-      <x:c r="C35" s="14"/>
+      <x:c r="A35" s="7"/>
+      <x:c r="B35" s="7"/>
+      <x:c r="C35" s="7"/>
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1"/>
     <x:row r="37" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9945"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="18510" windowHeight="10620"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -19,144 +19,147 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="46">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="47">
+  <x:si>
+    <x:t>skill_fireball_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_explosion_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_fireball_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불로 된 구체를 만들어 날린다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적을 벨 수 있는 검기를 날린다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필살 파이어볼!!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AnimTrigger</x:t>
+  </x:si>
+  <x:si>
+    <x:t>특 급 대 폭 발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필살 익스플로젼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsAtk_Swing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_swing_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>풀 스윙</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>커피 마시기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>익스플로젼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일단 휘두르기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필살 파이어볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필살 휘두르기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Damage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필살 풀 스윙</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어볼!!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대 폭 발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CostMp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>검기 날리기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Special</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_skill_swing_01_special</x:t>
+  </x:si>
   <x:si>
     <x:t>Icon/icon_skill_fireball_02_special</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Icon_skill_swing_01_special</x:t>
+    <x:t>Icon/Icon_skill_explosion_01_special</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_skill_explosion_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_fireball_02_special</x:t>
+  </x:si>
+  <x:si>
+    <x:t>커피를 볶아 마신다. 모든 상태이상이 해제된다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/icon_skill_fireball_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_skill_swing_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_explosion_01_special</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_rest_coffee_01</x:t>
   </x:si>
   <x:si>
     <x:t>skill_normalSword_01</x:t>
   </x:si>
   <x:si>
     <x:t>skill_swing_01_special</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_rest_coffee_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>특 급 대 폭 발</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필살 파이어볼!!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MotionPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필살 익스플로젼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_skill_explosion_01_special</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_skill_explosion_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어볼!!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>익스플로젼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>커피 마시기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>풀 스윙</x:t>
-  </x:si>
-  <x:si>
-    <x:t>검기 날리기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대 폭 발</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Damage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필살 휘두르기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필살 풀 스윙</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Special</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일단 휘두르기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필살 파이어볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CostMp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불로 된 구체를 만들어 날린다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_fireball_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_explosion_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적을 벨 수 있는 검기를 날린다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_fireball_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_swing_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_explosion_01_special</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_fireball_02_special</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_skill_swing_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/icon_skill_fireball_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>커피를 볶아 마신다. 모든 상태이상이 해제된다.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -956,7 +959,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A1" s="10" t="s">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B1" s="10"/>
       <x:c r="C1" s="10"/>
@@ -971,28 +974,28 @@
     </x:row>
     <x:row r="2" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A2" s="10" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B2" s="10" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C2" s="10" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D2" s="11" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E2" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F2" s="11" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G2" s="11" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H2" s="11" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I2" s="11"/>
       <x:c r="J2" s="11"/>
@@ -1006,19 +1009,19 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D3" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E3" s="4" t="s">
         <x:v>8</x:v>
-      </x:c>
-      <x:c r="E3" s="4" t="s">
-        <x:v>7</x:v>
       </x:c>
       <x:c r="F3" s="11" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="G3" s="11" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H3" s="11" t="s">
         <x:v>11</x:v>
@@ -1029,13 +1032,13 @@
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="13" t="s">
-        <x:v>36</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B4" s="13" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="C4" s="13" t="s">
-        <x:v>35</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D4" s="11"/>
       <x:c r="E4" s="4"/>
@@ -1052,13 +1055,13 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="13" t="s">
-        <x:v>2</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B5" s="14" t="s">
-        <x:v>23</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C5" s="14" t="s">
-        <x:v>38</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D5" s="11"/>
       <x:c r="E5" s="4"/>
@@ -1075,13 +1078,13 @@
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="14" t="s">
-        <x:v>4</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B6" s="14" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C6" s="14" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D6" s="11"/>
       <x:c r="E6" s="4"/>
@@ -1098,18 +1101,20 @@
     </x:row>
     <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A7" s="8" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B7" s="8" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C7" s="8" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C7" s="8" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="D7" s="9" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E7" s="4"/>
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E7" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="F7" s="4">
         <x:v>10</x:v>
       </x:c>
@@ -1117,7 +1122,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
@@ -1129,18 +1134,20 @@
     </x:row>
     <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A8" s="8" t="s">
-        <x:v>39</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B8" s="8" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="C8" s="8" t="s">
-        <x:v>17</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D8" s="9" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E8" s="4"/>
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E8" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="F8" s="4">
         <x:v>30</x:v>
       </x:c>
@@ -1148,7 +1155,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="I8" s="4"/>
       <x:c r="J8" s="4"/>
@@ -1160,18 +1167,20 @@
     </x:row>
     <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A9" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="8" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C9" s="8" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D9" s="9" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E9" s="4"/>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E9" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="F9" s="4">
         <x:v>100</x:v>
       </x:c>
@@ -1179,7 +1188,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H9" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>
@@ -1191,18 +1200,20 @@
     </x:row>
     <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A10" s="15" t="s">
-        <x:v>3</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B10" s="15" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C10" s="15" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D10" s="9" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E10" s="4"/>
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E10" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="F10" s="4">
         <x:v>25</x:v>
       </x:c>
@@ -1210,7 +1221,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="H10" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I10" s="4"/>
       <x:c r="J10" s="4"/>
@@ -1222,18 +1233,20 @@
     </x:row>
     <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A11" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B11" s="15" t="s">
-        <x:v>32</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="15" t="s">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D11" s="9" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E11" s="4"/>
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E11" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="F11" s="4">
         <x:v>70</x:v>
       </x:c>
@@ -1241,7 +1254,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H11" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I11" s="4"/>
       <x:c r="J11" s="4"/>
@@ -1253,18 +1266,20 @@
     </x:row>
     <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A12" s="8" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B12" s="16" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C12" s="16" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C12" s="16" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="D12" s="9" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E12" s="4"/>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E12" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="F12" s="4">
         <x:v>200</x:v>
       </x:c>
@@ -1272,7 +1287,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="H12" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I12" s="4"/>
       <x:c r="J12" s="4"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="18510" windowHeight="10620"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="20925" windowHeight="11340"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -19,147 +19,153 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="47">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="49">
+  <x:si>
+    <x:t>skill_swing_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>특 급 대 폭 발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsAtk_Swing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필살 파이어볼!!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AnimTrigger</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필살 익스플로젼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_SkillList[Icon_SkillList_16]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_SkillList[Icon_SkillList_0]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_SkillList[Icon_SkillList_1]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_SpecialSkillList[Icon_SpecialSkillList_0]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_SpecialSkillList[Icon_SpecialSkillList_3]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_SpecialSkillList[Icon_SpecialSkillList_5]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_SkillList[Icon_SkillList_2]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_SkillList[Icon_SkillList_17]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Damage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대 폭 발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CostMp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필살 파이어볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필살 휘두르기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필살 풀 스윙</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Special</x:t>
+  </x:si>
+  <x:si>
+    <x:t>검기 날리기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어볼!!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일단 휘두르기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>풀 스윙</x:t>
+  </x:si>
+  <x:si>
+    <x:t>익스플로젼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>커피 마시기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불로 된 구체를 만들어 날린다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_fireball_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_explosion_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적을 벨 수 있는 검기를 날린다.</x:t>
+  </x:si>
   <x:si>
     <x:t>skill_fireball_01</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_explosion_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_fireball_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불로 된 구체를 만들어 날린다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적을 벨 수 있는 검기를 날린다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필살 파이어볼!!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AnimTrigger</x:t>
-  </x:si>
-  <x:si>
-    <x:t>특 급 대 폭 발</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필살 익스플로젼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsAtk_Swing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_swing_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>풀 스윙</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>커피 마시기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>익스플로젼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일단 휘두르기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필살 파이어볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필살 휘두르기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Damage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필살 풀 스윙</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어볼!!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대 폭 발</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CostMp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>검기 날리기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Special</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_skill_swing_01_special</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/icon_skill_fireball_02_special</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_skill_explosion_01_special</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_skill_explosion_01</x:t>
+    <x:t>skill_normalSword_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_rest_coffee_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_swing_01_special</x:t>
+  </x:si>
+  <x:si>
+    <x:t>커피를 볶아 마신다. 모든 상태이상이 해제된다.</x:t>
   </x:si>
   <x:si>
     <x:t>skill_fireball_02_special</x:t>
   </x:si>
   <x:si>
-    <x:t>커피를 볶아 마신다. 모든 상태이상이 해제된다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/icon_skill_fireball_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_skill_swing_01</x:t>
-  </x:si>
-  <x:si>
     <x:t>skill_explosion_01_special</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_rest_coffee_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_normalSword_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_swing_01_special</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -952,14 +958,14 @@
     <x:col min="1" max="1" width="23" style="3" customWidth="1"/>
     <x:col min="2" max="2" width="19.5703125" style="3" customWidth="1"/>
     <x:col min="3" max="3" width="50.7109375" style="3" customWidth="1"/>
-    <x:col min="4" max="4" width="35.85546875" style="2" customWidth="1"/>
+    <x:col min="4" max="4" width="57.14453125" style="2" customWidth="1"/>
     <x:col min="5" max="5" width="30.5703125" style="3" customWidth="1"/>
     <x:col min="6" max="7" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A1" s="10" t="s">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B1" s="10"/>
       <x:c r="C1" s="10"/>
@@ -974,19 +980,19 @@
     </x:row>
     <x:row r="2" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A2" s="10" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B2" s="10" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C2" s="10" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D2" s="11" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E2" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F2" s="11" t="s">
         <x:v>16</x:v>
@@ -995,7 +1001,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H2" s="11" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="I2" s="11"/>
       <x:c r="J2" s="11"/>
@@ -1003,28 +1009,28 @@
     </x:row>
     <x:row r="3" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D3" s="11" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E3" s="4" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D3" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E3" s="4" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="F3" s="11" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G3" s="11" t="s">
-        <x:v>30</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H3" s="11" t="s">
-        <x:v>11</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I3" s="11"/>
       <x:c r="J3" s="11"/>
@@ -1032,15 +1038,17 @@
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="13" t="s">
-        <x:v>0</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B4" s="13" t="s">
-        <x:v>25</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C4" s="13" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="11"/>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D4" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
       <x:c r="E4" s="4"/>
       <x:c r="F4" s="4"/>
       <x:c r="G4" s="4"/>
@@ -1055,15 +1063,17 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="13" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B5" s="14" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C5" s="14" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="11"/>
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="s">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="E5" s="4"/>
       <x:c r="F5" s="4"/>
       <x:c r="G5" s="4"/>
@@ -1081,12 +1091,14 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B6" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C6" s="14" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D6" s="11"/>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
       <x:c r="E6" s="4"/>
       <x:c r="F6" s="4"/>
       <x:c r="G6" s="4"/>
@@ -1101,19 +1113,19 @@
     </x:row>
     <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A7" s="8" t="s">
-        <x:v>14</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B7" s="8" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C7" s="8" t="s">
-        <x:v>22</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D7" s="9" t="s">
-        <x:v>42</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>10</x:v>
@@ -1122,7 +1134,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
@@ -1134,19 +1146,19 @@
     </x:row>
     <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A8" s="8" t="s">
-        <x:v>2</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B8" s="8" t="s">
-        <x:v>25</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C8" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D8" s="9" t="s">
-        <x:v>41</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>30</x:v>
@@ -1155,7 +1167,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I8" s="4"/>
       <x:c r="J8" s="4"/>
@@ -1167,19 +1179,19 @@
     </x:row>
     <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A9" s="8" t="s">
-        <x:v>1</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B9" s="8" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C9" s="8" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C9" s="8" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="D9" s="9" t="s">
-        <x:v>38</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F9" s="4">
         <x:v>100</x:v>
@@ -1188,7 +1200,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H9" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>
@@ -1200,19 +1212,19 @@
     </x:row>
     <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A10" s="15" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B10" s="15" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C10" s="15" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D10" s="9" t="s">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E10" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F10" s="4">
         <x:v>25</x:v>
@@ -1221,7 +1233,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="H10" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="I10" s="4"/>
       <x:c r="J10" s="4"/>
@@ -1233,19 +1245,19 @@
     </x:row>
     <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A11" s="8" t="s">
-        <x:v>39</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B11" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="15" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D11" s="9" t="s">
-        <x:v>36</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E11" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F11" s="4">
         <x:v>70</x:v>
@@ -1254,7 +1266,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H11" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="I11" s="4"/>
       <x:c r="J11" s="4"/>
@@ -1266,19 +1278,19 @@
     </x:row>
     <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A12" s="8" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B12" s="16" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C12" s="16" t="s">
-        <x:v>9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D12" s="9" t="s">
-        <x:v>37</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E12" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F12" s="4">
         <x:v>200</x:v>
@@ -1287,7 +1299,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="H12" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="I12" s="4"/>
       <x:c r="J12" s="4"/>
